--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_coquimbo.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:25</t>
+    <t xml:space="preserve">2026-09-24 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -990,19 +990,19 @@
         <v>29</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="21">
@@ -1013,19 +1013,19 @@
         <v>29</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -1036,16 +1036,16 @@
         <v>29</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.13</v>
@@ -1062,13 +1062,13 @@
         <v>-0.64</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.23</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_coquimbo.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:15</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_coquimbo.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
